--- a/pipeline/geo/geo_lookup.xlsx
+++ b/pipeline/geo/geo_lookup.xlsx
@@ -12774,7 +12774,7 @@
       </x:c>
       <x:c r="B1029" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">London</x:t>
+          <x:t xml:space="preserve">Nottinghamshire</x:t>
         </x:is>
       </x:c>
     </x:row>
